--- a/test-data/locators.xlsx
+++ b/test-data/locators.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project1\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\newproject\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813C97A0-75AE-4087-852C-6FA833E64CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB0C765-BE50-422D-AA7C-B245C603A1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>ElementName</t>
   </si>
@@ -39,22 +39,28 @@
     <t>xpath</t>
   </si>
   <si>
-    <t>popupclose</t>
-  </si>
-  <si>
-    <t>//span[@class='commonModal__close']</t>
-  </si>
-  <si>
-    <t>//ul[@class='makeFlex font12 headerIconsGap']/li</t>
-  </si>
-  <si>
-    <t>optionslist</t>
-  </si>
-  <si>
-    <t>//p[@data-cy='checkInDate']</t>
-  </si>
-  <si>
-    <t>checkindate</t>
+    <t>//*[@id="usernameAdmin"]</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>//*[@id="passwordAdmin"]</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>//*[@id="btnAdminLogin"]</t>
+  </si>
+  <si>
+    <t>Rbuttom</t>
+  </si>
+  <si>
+    <t>//*[@id="adminLogin"]/div[7]/div/label/div</t>
   </si>
 </sst>
 </file>
@@ -372,15 +378,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,37 +397,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/locators.xlsx
+++ b/test-data/locators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\newproject\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB0C765-BE50-422D-AA7C-B245C603A1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA760375-B3C2-45E5-8747-936BBECEE7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>ElementName</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>//*[@id="adminLogin"]/div[7]/div/label/div</t>
+  </si>
+  <si>
+    <t>//*[@id="dropdownMenuButton1"]</t>
+  </si>
+  <si>
+    <t>profileicon</t>
   </si>
 </sst>
 </file>
@@ -378,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -441,6 +447,17 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/locators.xlsx
+++ b/test-data/locators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\newproject\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA760375-B3C2-45E5-8747-936BBECEE7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC38ED1-9D9D-4C41-91C1-15D03967DB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,13 +60,13 @@
     <t>Rbuttom</t>
   </si>
   <si>
-    <t>//*[@id="adminLogin"]/div[7]/div/label/div</t>
-  </si>
-  <si>
     <t>//*[@id="dropdownMenuButton1"]</t>
   </si>
   <si>
     <t>profileicon</t>
+  </si>
+  <si>
+    <t>//div[@class='check-border']</t>
   </si>
 </sst>
 </file>
@@ -444,18 +444,18 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/locators.xlsx
+++ b/test-data/locators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\newproject\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC38ED1-9D9D-4C41-91C1-15D03967DB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173DE9E0-B570-4882-A81A-AE7FA2DB9711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>ElementName</t>
   </si>
@@ -67,6 +67,42 @@
   </si>
   <si>
     <t>//div[@class='check-border']</t>
+  </si>
+  <si>
+    <t>//span[normalize-space()='Account']</t>
+  </si>
+  <si>
+    <t>Accountoptionclick</t>
+  </si>
+  <si>
+    <t>//a[normalize-space()='General settings']</t>
+  </si>
+  <si>
+    <t>generalsettingsclick</t>
+  </si>
+  <si>
+    <t>//h2[normalize-space()='General settings']</t>
+  </si>
+  <si>
+    <t>verifytitlegeneralsettings</t>
+  </si>
+  <si>
+    <t>//div[@role='tabpanel']//p[1]</t>
+  </si>
+  <si>
+    <t>supportemailaddresslabel</t>
+  </si>
+  <si>
+    <t>cancelbutton</t>
+  </si>
+  <si>
+    <t>//a[normalize-space()='Cancel']</t>
+  </si>
+  <si>
+    <t>//button[@id='submit']</t>
+  </si>
+  <si>
+    <t>submitbutton</t>
   </si>
 </sst>
 </file>
@@ -384,10 +420,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.33203125" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.77734375" bestFit="1" customWidth="1"/>
   </cols>
@@ -458,7 +494,74 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>